--- a/manuals/Hi-sAFe -V4.4 - Parameters and outputs.xlsx
+++ b/manuals/Hi-sAFe -V4.4 - Parameters and outputs.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" firstSheet="2" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="sim - simulation" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11245" uniqueCount="4201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11258" uniqueCount="4201">
   <si>
     <t>thick</t>
   </si>
@@ -11881,12 +11881,6 @@
     <t>Threshold of effective temperature for cumulating flowering degree day</t>
   </si>
   <si>
-    <t xml:space="preserve">fruitCarbonStressDayStart </t>
-  </si>
-  <si>
-    <t xml:space="preserve">First day for carbon stress calculation for fruits </t>
-  </si>
-  <si>
     <t>frostDamageActivation</t>
   </si>
   <si>
@@ -12735,6 +12729,12 @@
   </si>
   <si>
     <t>Cold temperature accumulation option for budburst triggered</t>
+  </si>
+  <si>
+    <t>fruitCarbonStressDateStart</t>
+  </si>
+  <si>
+    <t>Date to start accumulation of fruit carbon stress</t>
   </si>
 </sst>
 </file>
@@ -13505,7 +13505,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -14054,6 +14054,9 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="199">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -14613,19 +14616,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="126" t="s">
+        <v>4046</v>
+      </c>
+      <c r="B3" s="122" t="s">
+        <v>4073</v>
+      </c>
+      <c r="C3" s="126" t="s">
+        <v>4072</v>
+      </c>
+      <c r="D3" s="174" t="s">
         <v>4048</v>
       </c>
-      <c r="B3" s="122" t="s">
-        <v>4075</v>
-      </c>
-      <c r="C3" s="126" t="s">
-        <v>4074</v>
-      </c>
-      <c r="D3" s="174" t="s">
-        <v>4050</v>
-      </c>
       <c r="E3" s="101" t="s">
-        <v>4051</v>
+        <v>4049</v>
       </c>
       <c r="F3" s="101" t="s">
         <v>1295</v>
@@ -14636,19 +14639,19 @@
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="126" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B4" s="122" t="s">
+        <v>4051</v>
+      </c>
+      <c r="C4" s="126" t="s">
+        <v>4072</v>
+      </c>
+      <c r="D4" s="174" t="s">
+        <v>4050</v>
+      </c>
+      <c r="E4" s="101" t="s">
         <v>4049</v>
-      </c>
-      <c r="B4" s="122" t="s">
-        <v>4053</v>
-      </c>
-      <c r="C4" s="126" t="s">
-        <v>4074</v>
-      </c>
-      <c r="D4" s="174" t="s">
-        <v>4052</v>
-      </c>
-      <c r="E4" s="101" t="s">
-        <v>4051</v>
       </c>
       <c r="F4" s="101" t="s">
         <v>1295</v>
@@ -14734,7 +14737,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="118" t="s">
-        <v>4114</v>
+        <v>4112</v>
       </c>
       <c r="B9" s="119"/>
       <c r="C9" s="118"/>
@@ -14745,16 +14748,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="126" t="s">
-        <v>4054</v>
+        <v>4052</v>
       </c>
       <c r="B10" s="122" t="s">
-        <v>4062</v>
+        <v>4060</v>
       </c>
       <c r="C10" s="126" t="s">
         <v>1295</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>4060</v>
+        <v>4058</v>
       </c>
       <c r="E10" s="101" t="s">
         <v>3900</v>
@@ -14768,16 +14771,16 @@
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="127" t="s">
-        <v>4055</v>
+        <v>4053</v>
       </c>
       <c r="B11" s="122" t="s">
-        <v>4063</v>
+        <v>4061</v>
       </c>
       <c r="C11" s="126" t="s">
         <v>1295</v>
       </c>
       <c r="D11" s="90" t="s">
-        <v>4064</v>
+        <v>4062</v>
       </c>
       <c r="E11" s="101" t="s">
         <v>3900</v>
@@ -14791,16 +14794,16 @@
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="126" t="s">
-        <v>4098</v>
+        <v>4096</v>
       </c>
       <c r="B12" s="122" t="s">
-        <v>4061</v>
+        <v>4059</v>
       </c>
       <c r="C12" s="126" t="s">
         <v>1295</v>
       </c>
       <c r="D12" s="90" t="s">
-        <v>4102</v>
+        <v>4100</v>
       </c>
       <c r="E12" s="101" t="s">
         <v>3900</v>
@@ -14817,7 +14820,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="118" t="s">
-        <v>4115</v>
+        <v>4113</v>
       </c>
       <c r="B14" s="119"/>
       <c r="C14" s="118"/>
@@ -14828,16 +14831,16 @@
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="126" t="s">
+        <v>4097</v>
+      </c>
+      <c r="B15" s="122" t="s">
+        <v>4098</v>
+      </c>
+      <c r="C15" s="126" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D15" s="90" t="s">
         <v>4099</v>
-      </c>
-      <c r="B15" s="122" t="s">
-        <v>4100</v>
-      </c>
-      <c r="C15" s="126" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D15" s="90" t="s">
-        <v>4101</v>
       </c>
       <c r="E15" s="101" t="s">
         <v>3900</v>
@@ -14851,16 +14854,16 @@
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="127" t="s">
+        <v>4172</v>
+      </c>
+      <c r="B17" s="122" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C17" s="126" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D17" s="90" t="s">
         <v>4174</v>
-      </c>
-      <c r="B17" s="122" t="s">
-        <v>4175</v>
-      </c>
-      <c r="C17" s="126" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D17" s="90" t="s">
-        <v>4176</v>
       </c>
       <c r="E17" s="101" t="s">
         <v>3900</v>
@@ -19444,16 +19447,16 @@
         <v>1293</v>
       </c>
       <c r="C245" t="s">
-        <v>3930</v>
+        <v>3928</v>
       </c>
       <c r="D245" s="134" t="s">
         <v>124</v>
       </c>
       <c r="E245" s="73" t="s">
-        <v>3931</v>
+        <v>3929</v>
       </c>
       <c r="F245" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -25641,7 +25644,7 @@
         <v>1381</v>
       </c>
       <c r="C609" s="171" t="s">
-        <v>3947</v>
+        <v>3945</v>
       </c>
       <c r="D609" s="172" t="s">
         <v>3846</v>
@@ -25658,7 +25661,7 @@
         <v>1381</v>
       </c>
       <c r="C610" s="171" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
       <c r="D610" s="172" t="s">
         <v>3858</v>
@@ -25760,7 +25763,7 @@
         <v>1381</v>
       </c>
       <c r="C616" s="171" t="s">
-        <v>3949</v>
+        <v>3947</v>
       </c>
       <c r="D616" s="172" t="s">
         <v>3869</v>
@@ -25777,7 +25780,7 @@
         <v>1381</v>
       </c>
       <c r="C617" s="171" t="s">
-        <v>3950</v>
+        <v>3948</v>
       </c>
       <c r="D617" s="172" t="s">
         <v>3870</v>
@@ -45155,13 +45158,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="91" t="s">
-        <v>4185</v>
+        <v>4183</v>
       </c>
       <c r="B24" s="109" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="C24" s="98" t="s">
-        <v>4192</v>
+        <v>4190</v>
       </c>
       <c r="D24" s="99">
         <v>0.45</v>
@@ -45181,13 +45184,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="91" t="s">
-        <v>4186</v>
+        <v>4184</v>
       </c>
       <c r="B25" s="109" t="s">
-        <v>4193</v>
+        <v>4191</v>
       </c>
       <c r="C25" s="98" t="s">
-        <v>4194</v>
+        <v>4192</v>
       </c>
       <c r="D25" s="99">
         <v>50.4</v>
@@ -45196,7 +45199,7 @@
         <v>1721</v>
       </c>
       <c r="F25" s="107" t="s">
-        <v>4195</v>
+        <v>4193</v>
       </c>
       <c r="G25" s="107">
         <v>100</v>
@@ -45207,13 +45210,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="91" t="s">
-        <v>4187</v>
+        <v>4185</v>
       </c>
       <c r="B26" s="109" t="s">
-        <v>4196</v>
+        <v>4194</v>
       </c>
       <c r="C26" s="98" t="s">
-        <v>4197</v>
+        <v>4195</v>
       </c>
       <c r="D26" s="99">
         <v>3.0000000000000001E-3</v>
@@ -45233,10 +45236,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="91" t="s">
-        <v>4188</v>
+        <v>4186</v>
       </c>
       <c r="B27" s="109" t="s">
-        <v>4198</v>
+        <v>4196</v>
       </c>
       <c r="C27" s="192" t="s">
         <v>1295</v>
@@ -45259,10 +45262,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="91" t="s">
-        <v>4189</v>
+        <v>4187</v>
       </c>
       <c r="B28" s="109" t="s">
-        <v>4196</v>
+        <v>4194</v>
       </c>
       <c r="C28" s="192" t="s">
         <v>1295</v>
@@ -45285,10 +45288,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="91" t="s">
-        <v>4190</v>
+        <v>4188</v>
       </c>
       <c r="B29" s="109" t="s">
-        <v>4199</v>
+        <v>4197</v>
       </c>
       <c r="C29" s="98" t="s">
         <v>194</v>
@@ -45928,7 +45931,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="86" t="s">
-        <v>4116</v>
+        <v>4114</v>
       </c>
       <c r="B57" s="87"/>
       <c r="C57" s="88"/>
@@ -46195,7 +46198,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="86" t="s">
-        <v>4117</v>
+        <v>4115</v>
       </c>
       <c r="B69" s="87"/>
       <c r="C69" s="88"/>
@@ -46290,7 +46293,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="86" t="s">
-        <v>4118</v>
+        <v>4116</v>
       </c>
       <c r="B74" s="87"/>
       <c r="C74" s="88"/>
@@ -46314,16 +46317,16 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="91" t="s">
+        <v>4085</v>
+      </c>
+      <c r="B76" s="92" t="s">
         <v>4087</v>
       </c>
-      <c r="B76" s="92" t="s">
-        <v>4089</v>
-      </c>
       <c r="C76" s="92" t="s">
         <v>1295</v>
       </c>
       <c r="D76" s="99" t="s">
-        <v>4088</v>
+        <v>4086</v>
       </c>
       <c r="E76" s="96" t="s">
         <v>3900</v>
@@ -46968,10 +46971,10 @@
     </row>
     <row r="8" spans="1:8" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="39" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>4167</v>
+        <v>4165</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>2511</v>
@@ -47292,7 +47295,7 @@
     </row>
     <row r="21" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>4171</v>
+        <v>4169</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>2562</v>
@@ -47318,7 +47321,7 @@
     </row>
     <row r="22" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>4172</v>
+        <v>4170</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>2564</v>
@@ -47434,10 +47437,10 @@
     </row>
     <row r="27" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
-        <v>4177</v>
+        <v>4175</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>4178</v>
+        <v>4176</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>1516</v>
@@ -47455,15 +47458,15 @@
         <v>1</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>4173</v>
+        <v>4171</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="39" t="s">
-        <v>4179</v>
+        <v>4177</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>4180</v>
+        <v>4178</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>1516</v>
@@ -47655,7 +47658,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>4168</v>
+        <v>4166</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>1097</v>
@@ -47681,7 +47684,7 @@
         <v>50</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>4169</v>
+        <v>4167</v>
       </c>
       <c r="C37" s="44" t="s">
         <v>1631</v>
@@ -47707,7 +47710,7 @@
         <v>51</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>4170</v>
+        <v>4168</v>
       </c>
       <c r="C38" s="44" t="s">
         <v>1631</v>
@@ -48560,7 +48563,7 @@
     </row>
     <row r="72" spans="1:8" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="193" t="s">
-        <v>4121</v>
+        <v>4119</v>
       </c>
       <c r="B72" s="193"/>
       <c r="C72" s="193"/>
@@ -48572,16 +48575,16 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="58" t="s">
-        <v>4119</v>
+        <v>4117</v>
       </c>
       <c r="B73" s="59" t="s">
-        <v>4123</v>
+        <v>4121</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>1516</v>
       </c>
       <c r="D73" s="126" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="E73" s="29" t="s">
         <v>1749</v>
@@ -48596,16 +48599,16 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="58" t="s">
-        <v>4120</v>
+        <v>4118</v>
       </c>
       <c r="B74" s="59" t="s">
-        <v>4124</v>
+        <v>4122</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>1516</v>
       </c>
       <c r="D74" s="126" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="E74" s="29" t="s">
         <v>1749</v>
@@ -51110,7 +51113,7 @@
     </row>
     <row r="125" spans="1:8" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="193" t="s">
-        <v>4125</v>
+        <v>4123</v>
       </c>
       <c r="B125" s="193"/>
       <c r="C125" s="193"/>
@@ -51202,7 +51205,7 @@
     </row>
     <row r="130" spans="1:8" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="193" t="s">
-        <v>4126</v>
+        <v>4124</v>
       </c>
       <c r="B130" s="193"/>
       <c r="C130" s="193"/>
@@ -52288,10 +52291,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="127" t="s">
-        <v>4040</v>
+        <v>4038</v>
       </c>
       <c r="B32" s="123" t="s">
-        <v>4041</v>
+        <v>4039</v>
       </c>
       <c r="C32" s="144" t="s">
         <v>17</v>
@@ -52387,20 +52390,20 @@
       <c r="B37" s="123" t="s">
         <v>165</v>
       </c>
-      <c r="C37" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="96">
-        <v>61</v>
+      <c r="C37" s="127" t="s">
+        <v>4070</v>
+      </c>
+      <c r="D37" s="194" t="s">
+        <v>4069</v>
       </c>
       <c r="E37" s="96" t="s">
-        <v>1749</v>
-      </c>
-      <c r="F37" s="96">
-        <v>1</v>
-      </c>
-      <c r="G37" s="96">
-        <v>365</v>
+        <v>3900</v>
+      </c>
+      <c r="F37" s="182" t="s">
+        <v>4069</v>
+      </c>
+      <c r="G37" s="182" t="s">
+        <v>4102</v>
       </c>
       <c r="H37" s="164" t="s">
         <v>2498</v>
@@ -52545,46 +52548,46 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="127" t="s">
-        <v>3933</v>
+        <v>3931</v>
       </c>
       <c r="B44" s="123" t="s">
-        <v>4200</v>
+        <v>4198</v>
       </c>
       <c r="C44" s="144" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
       <c r="H44" s="166"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="127" t="s">
-        <v>3934</v>
+        <v>3932</v>
       </c>
       <c r="B45" s="123" t="s">
-        <v>3942</v>
-      </c>
-      <c r="C45" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="D45" s="96">
-        <v>244</v>
+        <v>3940</v>
+      </c>
+      <c r="C45" s="127" t="s">
+        <v>4070</v>
+      </c>
+      <c r="D45" s="194" t="s">
+        <v>4069</v>
       </c>
       <c r="E45" s="96" t="s">
-        <v>1749</v>
-      </c>
-      <c r="F45" s="96">
-        <v>1</v>
-      </c>
-      <c r="G45" s="96">
-        <v>365</v>
+        <v>3900</v>
+      </c>
+      <c r="F45" s="182" t="s">
+        <v>4069</v>
+      </c>
+      <c r="G45" s="182" t="s">
+        <v>4102</v>
       </c>
       <c r="H45" s="166"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="127" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
       <c r="B46" s="123" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
       <c r="C46" s="144" t="s">
         <v>1467</v>
@@ -52605,10 +52608,10 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="127" t="s">
-        <v>3936</v>
+        <v>3934</v>
       </c>
       <c r="B47" s="123" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
       <c r="C47" s="144" t="s">
         <v>1468</v>
@@ -52629,10 +52632,10 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="127" t="s">
-        <v>3937</v>
+        <v>3935</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="C48" s="144" t="s">
         <v>1295</v>
@@ -52644,15 +52647,15 @@
         <v>1721</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="127" t="s">
-        <v>3938</v>
+        <v>3936</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="C49" s="144" t="s">
         <v>1295</v>
@@ -52664,15 +52667,15 @@
         <v>1721</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="127" t="s">
-        <v>3939</v>
+        <v>3937</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="C50" s="144" t="s">
         <v>1295</v>
@@ -52684,15 +52687,15 @@
         <v>1721</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="127" t="s">
-        <v>3940</v>
+        <v>3938</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="C51" s="144" t="s">
         <v>1295</v>
@@ -52704,7 +52707,7 @@
         <v>1721</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -52883,7 +52886,7 @@
         <v>177</v>
       </c>
       <c r="B61" s="123" t="s">
-        <v>4047</v>
+        <v>4045</v>
       </c>
       <c r="C61" s="144" t="s">
         <v>1295</v>
@@ -52973,7 +52976,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="118" t="s">
-        <v>4046</v>
+        <v>4044</v>
       </c>
       <c r="B66" s="119"/>
       <c r="C66" s="140"/>
@@ -53172,11 +53175,11 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="127" t="s">
-        <v>4042</v>
+        <v>4040</v>
       </c>
       <c r="B75" s="123"/>
       <c r="C75" s="144" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
       <c r="D75" s="96">
         <v>0</v>
@@ -53185,11 +53188,11 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="127" t="s">
-        <v>4043</v>
+        <v>4041</v>
       </c>
       <c r="B76" s="123"/>
       <c r="C76" s="144" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
       <c r="D76" s="96">
         <v>0</v>
@@ -53198,11 +53201,11 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="127" t="s">
-        <v>4045</v>
+        <v>4043</v>
       </c>
       <c r="B77" s="123"/>
       <c r="C77" s="144" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
       <c r="D77" s="96">
         <v>0</v>
@@ -53235,7 +53238,7 @@
     </row>
     <row r="79" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="127" t="s">
-        <v>4044</v>
+        <v>4042</v>
       </c>
       <c r="B79" s="123" t="s">
         <v>3252</v>
@@ -54556,20 +54559,20 @@
       <c r="B132" s="123" t="s">
         <v>3672</v>
       </c>
-      <c r="C132" s="145" t="s">
-        <v>63</v>
-      </c>
-      <c r="D132" s="96">
-        <v>1</v>
+      <c r="C132" s="127" t="s">
+        <v>4070</v>
+      </c>
+      <c r="D132" s="194" t="s">
+        <v>4069</v>
       </c>
       <c r="E132" s="96" t="s">
-        <v>1749</v>
-      </c>
-      <c r="F132" s="96">
-        <v>1</v>
-      </c>
-      <c r="G132" s="157" t="s">
-        <v>1295</v>
+        <v>3900</v>
+      </c>
+      <c r="F132" s="182" t="s">
+        <v>4069</v>
+      </c>
+      <c r="G132" s="182" t="s">
+        <v>4102</v>
       </c>
       <c r="H132" s="170" t="s">
         <v>3740</v>
@@ -54845,25 +54848,25 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="126" t="s">
-        <v>3917</v>
+        <v>4199</v>
       </c>
       <c r="B143" s="122" t="s">
-        <v>3918</v>
-      </c>
-      <c r="C143" s="145" t="s">
-        <v>63</v>
-      </c>
-      <c r="D143" s="96">
-        <v>92</v>
+        <v>4200</v>
+      </c>
+      <c r="C143" s="127" t="s">
+        <v>4070</v>
+      </c>
+      <c r="D143" s="194" t="s">
+        <v>4069</v>
       </c>
       <c r="E143" s="96" t="s">
-        <v>1749</v>
-      </c>
-      <c r="F143" s="96">
-        <v>0</v>
-      </c>
-      <c r="G143" s="96">
-        <v>365</v>
+        <v>3900</v>
+      </c>
+      <c r="F143" s="182" t="s">
+        <v>4069</v>
+      </c>
+      <c r="G143" s="182" t="s">
+        <v>4102</v>
       </c>
       <c r="H143" s="170"/>
     </row>
@@ -54922,7 +54925,7 @@
         <v>3684</v>
       </c>
       <c r="C146" s="145" t="s">
-        <v>3929</v>
+        <v>3927</v>
       </c>
       <c r="D146" s="96">
         <v>0.8</v>
@@ -55193,20 +55196,20 @@
       <c r="B159" s="122" t="s">
         <v>3731</v>
       </c>
-      <c r="C159" s="145" t="s">
-        <v>63</v>
-      </c>
-      <c r="D159" s="96">
-        <v>61</v>
+      <c r="C159" s="127" t="s">
+        <v>4070</v>
+      </c>
+      <c r="D159" s="194" t="s">
+        <v>4069</v>
       </c>
       <c r="E159" s="96" t="s">
-        <v>1749</v>
-      </c>
-      <c r="F159" s="96">
-        <v>1</v>
-      </c>
-      <c r="G159" s="157" t="s">
-        <v>1295</v>
+        <v>3900</v>
+      </c>
+      <c r="F159" s="182" t="s">
+        <v>4069</v>
+      </c>
+      <c r="G159" s="182" t="s">
+        <v>4102</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -55719,7 +55722,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="118" t="s">
-        <v>4091</v>
+        <v>4089</v>
       </c>
       <c r="B189" s="119"/>
       <c r="C189" s="140"/>
@@ -55732,10 +55735,10 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="126" t="s">
-        <v>4090</v>
+        <v>4088</v>
       </c>
       <c r="B190" s="92" t="s">
-        <v>4097</v>
+        <v>4095</v>
       </c>
       <c r="C190" s="90" t="s">
         <v>2511</v>
@@ -55758,10 +55761,10 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="126" t="s">
-        <v>4092</v>
+        <v>4090</v>
       </c>
       <c r="B191" s="92" t="s">
-        <v>4096</v>
+        <v>4094</v>
       </c>
       <c r="C191" s="90" t="s">
         <v>2511</v>
@@ -55784,7 +55787,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="126" t="s">
-        <v>4093</v>
+        <v>4091</v>
       </c>
       <c r="C192" s="145"/>
       <c r="D192" s="96">
@@ -55796,7 +55799,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="126" t="s">
-        <v>4094</v>
+        <v>4092</v>
       </c>
       <c r="C193" s="145"/>
       <c r="D193" s="96">
@@ -55808,7 +55811,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="126" t="s">
-        <v>4095</v>
+        <v>4093</v>
       </c>
       <c r="C194" s="145"/>
       <c r="D194" s="96">
@@ -59635,7 +59638,7 @@
         <v>612</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>4113</v>
+        <v>4111</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>485</v>
@@ -60842,7 +60845,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="20" t="s">
-        <v>4137</v>
+        <v>4135</v>
       </c>
       <c r="B195" s="13"/>
       <c r="C195" s="13"/>
@@ -60854,7 +60857,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>4127</v>
+        <v>4125</v>
       </c>
       <c r="B196" s="14" t="s">
         <v>225</v>
@@ -60883,7 +60886,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>4128</v>
+        <v>4126</v>
       </c>
       <c r="B197" s="14" t="s">
         <v>226</v>
@@ -60912,7 +60915,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>4129</v>
+        <v>4127</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>228</v>
@@ -60938,7 +60941,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>4130</v>
+        <v>4128</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>229</v>
@@ -60967,7 +60970,7 @@
     </row>
     <row r="200" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>4131</v>
+        <v>4129</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>230</v>
@@ -60996,7 +60999,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>4132</v>
+        <v>4130</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>231</v>
@@ -61022,7 +61025,7 @@
     </row>
     <row r="202" spans="1:9" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>4133</v>
+        <v>4131</v>
       </c>
       <c r="B202" s="10" t="s">
         <v>2567</v>
@@ -61048,7 +61051,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="20" t="s">
-        <v>4134</v>
+        <v>4132</v>
       </c>
       <c r="B204" s="13"/>
       <c r="C204" s="13"/>
@@ -61060,10 +61063,10 @@
     </row>
     <row r="205" spans="1:9" s="185" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="185" t="s">
-        <v>4135</v>
+        <v>4133</v>
       </c>
       <c r="B205" s="185" t="s">
-        <v>4136</v>
+        <v>4134</v>
       </c>
       <c r="C205" s="185" t="s">
         <v>1516</v>
@@ -61606,7 +61609,7 @@
     </row>
     <row r="2" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="126" t="s">
-        <v>4070</v>
+        <v>4068</v>
       </c>
       <c r="B2" s="122" t="s">
         <v>3899</v>
@@ -61629,33 +61632,33 @@
     </row>
     <row r="3" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="126" t="s">
-        <v>4076</v>
+        <v>4074</v>
       </c>
       <c r="B3" s="122" t="s">
-        <v>4073</v>
+        <v>4071</v>
       </c>
       <c r="C3" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D3" s="117" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="E3" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F3" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="90" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="91" t="s">
-        <v>4077</v>
+        <v>4075</v>
       </c>
       <c r="B4" s="92" t="s">
-        <v>4080</v>
+        <v>4078</v>
       </c>
       <c r="C4" s="92" t="s">
         <v>3518</v>
@@ -61675,10 +61678,10 @@
     </row>
     <row r="5" spans="1:8" s="90" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="91" t="s">
-        <v>4078</v>
+        <v>4076</v>
       </c>
       <c r="B5" s="97" t="s">
-        <v>4081</v>
+        <v>4079</v>
       </c>
       <c r="C5" s="93" t="s">
         <v>17</v>
@@ -61701,10 +61704,10 @@
     </row>
     <row r="6" spans="1:8" s="90" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="91" t="s">
-        <v>4079</v>
+        <v>4077</v>
       </c>
       <c r="B6" s="97" t="s">
-        <v>4082</v>
+        <v>4080</v>
       </c>
       <c r="C6" s="93" t="s">
         <v>17</v>
@@ -61727,10 +61730,10 @@
     </row>
     <row r="7" spans="1:8" s="90" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="91" t="s">
-        <v>4083</v>
+        <v>4081</v>
       </c>
       <c r="B7" s="97" t="s">
-        <v>4084</v>
+        <v>4082</v>
       </c>
       <c r="C7" s="93" t="s">
         <v>17</v>
@@ -61753,10 +61756,10 @@
     </row>
     <row r="8" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="126" t="s">
-        <v>4085</v>
+        <v>4083</v>
       </c>
       <c r="B8" s="122" t="s">
-        <v>4086</v>
+        <v>4084</v>
       </c>
       <c r="C8" s="127" t="s">
         <v>516</v>
@@ -61779,7 +61782,7 @@
     </row>
     <row r="9" spans="1:8" s="90" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="116" t="s">
-        <v>4065</v>
+        <v>4063</v>
       </c>
       <c r="B9" s="97" t="s">
         <v>2599</v>
@@ -61805,7 +61808,7 @@
     </row>
     <row r="10" spans="1:8" s="90" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="104" t="s">
-        <v>4066</v>
+        <v>4064</v>
       </c>
       <c r="B10" s="97" t="s">
         <v>2600</v>
@@ -61831,7 +61834,7 @@
     </row>
     <row r="11" spans="1:8" s="90" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="104" t="s">
-        <v>4067</v>
+        <v>4065</v>
       </c>
       <c r="B11" s="97" t="s">
         <v>2602</v>
@@ -61857,7 +61860,7 @@
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="104" t="s">
-        <v>4068</v>
+        <v>4066</v>
       </c>
       <c r="B12" s="97" t="s">
         <v>2601</v>
@@ -61883,7 +61886,7 @@
     </row>
     <row r="13" spans="1:8" s="90" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="104" t="s">
-        <v>4069</v>
+        <v>4067</v>
       </c>
       <c r="B13" s="97" t="s">
         <v>2603</v>
@@ -61919,7 +61922,7 @@
     </row>
     <row r="15" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="118" t="s">
-        <v>4138</v>
+        <v>4136</v>
       </c>
       <c r="B15" s="119"/>
       <c r="C15" s="118"/>
@@ -61930,10 +61933,10 @@
     </row>
     <row r="16" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="126" t="s">
-        <v>4139</v>
+        <v>4137</v>
       </c>
       <c r="B16" s="122" t="s">
-        <v>4142</v>
+        <v>4140</v>
       </c>
       <c r="C16" s="126" t="s">
         <v>2379</v>
@@ -61953,25 +61956,25 @@
     </row>
     <row r="17" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="126" t="s">
-        <v>4140</v>
+        <v>4138</v>
       </c>
       <c r="B17" s="122" t="s">
-        <v>4141</v>
+        <v>4139</v>
       </c>
       <c r="C17" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D17" s="117" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="E17" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F17" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G17" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
@@ -62003,7 +62006,7 @@
         <v>2379</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>4107</v>
+        <v>4105</v>
       </c>
       <c r="E20" s="96" t="s">
         <v>1749</v>
@@ -62026,7 +62029,7 @@
         <v>1494</v>
       </c>
       <c r="D21" s="91" t="s">
-        <v>4108</v>
+        <v>4106</v>
       </c>
       <c r="E21" s="96" t="s">
         <v>1721</v>
@@ -62049,7 +62052,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="90" t="s">
-        <v>4109</v>
+        <v>4107</v>
       </c>
       <c r="E22" s="96" t="s">
         <v>1721</v>
@@ -62069,33 +62072,33 @@
         <v>1490</v>
       </c>
       <c r="C23" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D23" s="117" t="s">
-        <v>4110</v>
+        <v>4108</v>
       </c>
       <c r="E23" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F23" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G23" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="126" t="s">
-        <v>4056</v>
+        <v>4054</v>
       </c>
       <c r="B24" s="122" t="s">
-        <v>4057</v>
+        <v>4055</v>
       </c>
       <c r="C24" s="126" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="D24" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E24" s="96" t="s">
         <v>3759</v>
@@ -62109,16 +62112,16 @@
     </row>
     <row r="25" spans="1:8" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
-        <v>4143</v>
+        <v>4141</v>
       </c>
       <c r="B25" s="122" t="s">
-        <v>4144</v>
+        <v>4142</v>
       </c>
       <c r="C25" s="126" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="D25" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E25" s="29" t="s">
         <v>1749</v>
@@ -62180,19 +62183,19 @@
         <v>1487</v>
       </c>
       <c r="C29" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D29" s="117" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="E29" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F29" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G29" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="126" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -62250,7 +62253,7 @@
     </row>
     <row r="33" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="118" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
       <c r="B33" s="118"/>
       <c r="C33" s="118"/>
@@ -62261,16 +62264,16 @@
     </row>
     <row r="34" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="126" t="s">
-        <v>4001</v>
+        <v>3999</v>
       </c>
       <c r="B34" s="122" t="s">
-        <v>4002</v>
+        <v>4000</v>
       </c>
       <c r="C34" s="126" t="s">
         <v>2379</v>
       </c>
       <c r="D34" s="90" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="E34" s="96" t="s">
         <v>1749</v>
@@ -62284,39 +62287,39 @@
     </row>
     <row r="35" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="126" t="s">
-        <v>4103</v>
+        <v>4101</v>
       </c>
       <c r="B35" s="122" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="C35" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D35" s="117" t="s">
-        <v>4110</v>
+        <v>4108</v>
       </c>
       <c r="E35" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F35" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G35" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="126" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="B36" s="122" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="C36" s="126" t="s">
         <v>3758</v>
       </c>
       <c r="D36" s="90" t="s">
-        <v>4038</v>
+        <v>4036</v>
       </c>
       <c r="E36" s="96" t="s">
         <v>1721</v>
@@ -62330,16 +62333,16 @@
     </row>
     <row r="37" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="126" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B37" s="122" t="s">
         <v>4181</v>
       </c>
-      <c r="B37" s="122" t="s">
-        <v>4183</v>
-      </c>
       <c r="C37" s="126" t="s">
-        <v>4182</v>
+        <v>4180</v>
       </c>
       <c r="D37" s="90" t="s">
-        <v>4039</v>
+        <v>4037</v>
       </c>
       <c r="E37" s="96" t="s">
         <v>3759</v>
@@ -62353,16 +62356,16 @@
     </row>
     <row r="38" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="126" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="B38" s="122" t="s">
+        <v>4033</v>
+      </c>
+      <c r="C38" s="126" t="s">
+        <v>4006</v>
+      </c>
+      <c r="D38" s="90" t="s">
         <v>4035</v>
-      </c>
-      <c r="C38" s="126" t="s">
-        <v>4008</v>
-      </c>
-      <c r="D38" s="90" t="s">
-        <v>4037</v>
       </c>
       <c r="E38" s="96" t="s">
         <v>3759</v>
@@ -62376,16 +62379,16 @@
     </row>
     <row r="39" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="126" t="s">
-        <v>4145</v>
+        <v>4143</v>
       </c>
       <c r="B39" s="122" t="s">
-        <v>4146</v>
+        <v>4144</v>
       </c>
       <c r="C39" s="126" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="D39" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E39" s="96" t="s">
         <v>3759</v>
@@ -62406,7 +62409,7 @@
     </row>
     <row r="41" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="118" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="B41" s="118"/>
       <c r="C41" s="118"/>
@@ -62417,16 +62420,16 @@
     </row>
     <row r="42" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="126" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="B42" s="122" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="C42" s="126" t="s">
         <v>2379</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="E42" s="96" t="s">
         <v>1749</v>
@@ -62440,39 +62443,39 @@
     </row>
     <row r="43" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="126" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="B43" s="122" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="C43" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D43" s="117" t="s">
-        <v>4110</v>
+        <v>4108</v>
       </c>
       <c r="E43" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F43" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G43" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="126" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="B44" s="122" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="C44" s="126" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="90" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="E44" s="96" t="s">
         <v>1721</v>
@@ -62486,16 +62489,16 @@
     </row>
     <row r="45" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="126" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="B45" s="122" t="s">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="C45" s="126" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="E45" s="96" t="s">
         <v>1721</v>
@@ -62509,16 +62512,16 @@
     </row>
     <row r="46" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="126" t="s">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="B46" s="122" t="s">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="C46" s="126" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="E46" s="96" t="s">
         <v>1721</v>
@@ -62532,16 +62535,16 @@
     </row>
     <row r="47" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="126" t="s">
-        <v>4022</v>
+        <v>4020</v>
       </c>
       <c r="B47" s="122" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="C47" s="126" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="90" t="s">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="E47" s="96" t="s">
         <v>1721</v>
@@ -62555,16 +62558,16 @@
     </row>
     <row r="48" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="126" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="B48" s="122" t="s">
-        <v>4036</v>
+        <v>4034</v>
       </c>
       <c r="C48" s="126" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="D48" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E48" s="96" t="s">
         <v>3759</v>
@@ -62578,16 +62581,16 @@
     </row>
     <row r="49" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="126" t="s">
-        <v>4147</v>
+        <v>4145</v>
       </c>
       <c r="B49" s="122" t="s">
-        <v>4148</v>
+        <v>4146</v>
       </c>
       <c r="C49" s="126" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="D49" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E49" s="96" t="s">
         <v>3759</v>
@@ -62608,7 +62611,7 @@
     </row>
     <row r="51" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="118" t="s">
-        <v>4025</v>
+        <v>4023</v>
       </c>
       <c r="B51" s="118"/>
       <c r="C51" s="118"/>
@@ -62619,10 +62622,10 @@
     </row>
     <row r="52" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="126" t="s">
-        <v>4027</v>
+        <v>4025</v>
       </c>
       <c r="B52" s="122" t="s">
-        <v>4031</v>
+        <v>4029</v>
       </c>
       <c r="C52" s="126" t="s">
         <v>2379</v>
@@ -62642,33 +62645,33 @@
     </row>
     <row r="53" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="126" t="s">
-        <v>4028</v>
+        <v>4026</v>
       </c>
       <c r="B53" s="122" t="s">
-        <v>4032</v>
+        <v>4030</v>
       </c>
       <c r="C53" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D53" s="117" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="E53" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F53" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G53" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="126" t="s">
-        <v>4029</v>
+        <v>4027</v>
       </c>
       <c r="B54" s="122" t="s">
-        <v>4033</v>
+        <v>4031</v>
       </c>
       <c r="C54" s="126" t="s">
         <v>17</v>
@@ -62688,13 +62691,13 @@
     </row>
     <row r="55" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="126" t="s">
-        <v>4030</v>
+        <v>4028</v>
       </c>
       <c r="B55" s="122" t="s">
-        <v>4034</v>
+        <v>4032</v>
       </c>
       <c r="C55" s="126" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="D55" s="90">
         <v>0</v>
@@ -62711,16 +62714,16 @@
     </row>
     <row r="56" spans="1:8" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="58" t="s">
-        <v>4149</v>
+        <v>4147</v>
       </c>
       <c r="B56" s="122" t="s">
-        <v>4150</v>
+        <v>4148</v>
       </c>
       <c r="C56" s="126" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="D56" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E56" s="29" t="s">
         <v>1749</v>
@@ -62742,7 +62745,7 @@
     </row>
     <row r="58" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="118" t="s">
-        <v>4026</v>
+        <v>4024</v>
       </c>
       <c r="B58" s="118"/>
       <c r="C58" s="118"/>
@@ -62753,10 +62756,10 @@
     </row>
     <row r="59" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="126" t="s">
-        <v>3925</v>
+        <v>3923</v>
       </c>
       <c r="B59" s="122" t="s">
-        <v>3926</v>
+        <v>3924</v>
       </c>
       <c r="C59" s="126" t="s">
         <v>2379</v>
@@ -62779,10 +62782,10 @@
         <v>3905</v>
       </c>
       <c r="B60" s="122" t="s">
-        <v>3928</v>
+        <v>3926</v>
       </c>
       <c r="C60" s="126" t="s">
-        <v>3992</v>
+        <v>3990</v>
       </c>
       <c r="D60" s="90">
         <v>1</v>
@@ -62802,33 +62805,33 @@
         <v>3904</v>
       </c>
       <c r="B61" s="122" t="s">
-        <v>3927</v>
+        <v>3925</v>
       </c>
       <c r="C61" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D61" s="117" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="E61" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F61" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G61" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="126" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B62" s="122" t="s">
+        <v>3996</v>
+      </c>
+      <c r="C62" s="126" t="s">
         <v>3993</v>
-      </c>
-      <c r="B62" s="122" t="s">
-        <v>3998</v>
-      </c>
-      <c r="C62" s="126" t="s">
-        <v>3995</v>
       </c>
       <c r="D62" s="90">
         <v>1500</v>
@@ -62845,13 +62848,13 @@
     </row>
     <row r="63" spans="1:8" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="126" t="s">
+        <v>3992</v>
+      </c>
+      <c r="B63" s="122" t="s">
+        <v>3997</v>
+      </c>
+      <c r="C63" s="126" t="s">
         <v>3994</v>
-      </c>
-      <c r="B63" s="122" t="s">
-        <v>3999</v>
-      </c>
-      <c r="C63" s="126" t="s">
-        <v>3996</v>
       </c>
       <c r="D63" s="90">
         <v>150</v>
@@ -62871,7 +62874,7 @@
         <v>3690</v>
       </c>
       <c r="B64" s="122" t="s">
-        <v>3997</v>
+        <v>3995</v>
       </c>
       <c r="C64" s="126" t="s">
         <v>3760</v>
@@ -62891,16 +62894,16 @@
     </row>
     <row r="65" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="126" t="s">
-        <v>4058</v>
+        <v>4056</v>
       </c>
       <c r="B65" s="122" t="s">
-        <v>4059</v>
+        <v>4057</v>
       </c>
       <c r="C65" s="126" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="D65" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E65" s="96" t="s">
         <v>3759</v>
@@ -62914,16 +62917,16 @@
     </row>
     <row r="66" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="126" t="s">
-        <v>4151</v>
+        <v>4149</v>
       </c>
       <c r="B66" s="122" t="s">
-        <v>4152</v>
+        <v>4150</v>
       </c>
       <c r="C66" s="126" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="D66" s="90" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="E66" s="96" t="s">
         <v>3759</v>
@@ -62944,7 +62947,7 @@
     </row>
     <row r="68" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="118" t="s">
-        <v>3921</v>
+        <v>3919</v>
       </c>
       <c r="B68" s="118"/>
       <c r="C68" s="118"/>
@@ -62955,25 +62958,25 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3922</v>
+        <v>3920</v>
       </c>
       <c r="B69" s="122" t="s">
-        <v>3923</v>
+        <v>3921</v>
       </c>
       <c r="C69" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D69" s="117" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="E69" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F69" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G69" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
@@ -62985,7 +62988,7 @@
     </row>
     <row r="71" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="118" t="s">
-        <v>3951</v>
+        <v>3949</v>
       </c>
       <c r="B71" s="119"/>
       <c r="C71" s="118"/>
@@ -62996,13 +62999,13 @@
     </row>
     <row r="72" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="126" t="s">
-        <v>3952</v>
+        <v>3950</v>
       </c>
       <c r="B72" s="122" t="s">
-        <v>3961</v>
+        <v>3959</v>
       </c>
       <c r="C72" s="126" t="s">
-        <v>3960</v>
+        <v>3958</v>
       </c>
       <c r="D72" s="90">
         <v>1</v>
@@ -63019,10 +63022,10 @@
     </row>
     <row r="73" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="126" t="s">
-        <v>3953</v>
+        <v>3951</v>
       </c>
       <c r="B73" s="122" t="s">
-        <v>3962</v>
+        <v>3960</v>
       </c>
       <c r="C73" s="126" t="s">
         <v>2379</v>
@@ -63042,13 +63045,13 @@
     </row>
     <row r="74" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="126" t="s">
-        <v>3954</v>
+        <v>3952</v>
       </c>
       <c r="B74" s="122" t="s">
-        <v>3966</v>
+        <v>3964</v>
       </c>
       <c r="C74" s="126" t="s">
-        <v>3965</v>
+        <v>3963</v>
       </c>
       <c r="D74" s="90">
         <v>1</v>
@@ -63065,10 +63068,10 @@
     </row>
     <row r="75" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="126" t="s">
-        <v>3955</v>
+        <v>3953</v>
       </c>
       <c r="B75" s="122" t="s">
-        <v>3967</v>
+        <v>3965</v>
       </c>
       <c r="C75" s="126" t="s">
         <v>17</v>
@@ -63088,10 +63091,10 @@
     </row>
     <row r="76" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="126" t="s">
-        <v>3956</v>
+        <v>3954</v>
       </c>
       <c r="B76" s="126" t="s">
-        <v>3970</v>
+        <v>3968</v>
       </c>
       <c r="D76" s="90">
         <v>0.5</v>
@@ -63108,10 +63111,10 @@
     </row>
     <row r="77" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="126" t="s">
-        <v>3957</v>
+        <v>3955</v>
       </c>
       <c r="B77" s="122" t="s">
-        <v>3968</v>
+        <v>3966</v>
       </c>
       <c r="C77" s="126" t="s">
         <v>100</v>
@@ -63131,39 +63134,39 @@
     </row>
     <row r="78" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="126" t="s">
-        <v>3958</v>
+        <v>3956</v>
       </c>
       <c r="B78" s="122" t="s">
-        <v>3963</v>
+        <v>3961</v>
       </c>
       <c r="C78" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D78" s="117" t="s">
-        <v>4111</v>
+        <v>4109</v>
       </c>
       <c r="E78" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F78" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G78" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="126" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
       <c r="B79" s="122" t="s">
-        <v>3964</v>
+        <v>3962</v>
       </c>
       <c r="C79" s="126" t="s">
         <v>100</v>
       </c>
       <c r="D79" s="90" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
       <c r="E79" s="96" t="s">
         <v>1749</v>
@@ -63184,7 +63187,7 @@
     </row>
     <row r="81" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="118" t="s">
-        <v>3971</v>
+        <v>3969</v>
       </c>
       <c r="B81" s="119"/>
       <c r="C81" s="118"/>
@@ -63195,13 +63198,13 @@
     </row>
     <row r="82" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="126" t="s">
-        <v>3972</v>
+        <v>3970</v>
       </c>
       <c r="B82" s="122" t="s">
-        <v>3973</v>
+        <v>3971</v>
       </c>
       <c r="C82" s="126" t="s">
-        <v>3960</v>
+        <v>3958</v>
       </c>
       <c r="D82" s="90">
         <v>1</v>
@@ -63218,10 +63221,10 @@
     </row>
     <row r="83" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="126" t="s">
-        <v>3974</v>
+        <v>3972</v>
       </c>
       <c r="B83" s="122" t="s">
-        <v>3975</v>
+        <v>3973</v>
       </c>
       <c r="C83" s="126" t="s">
         <v>2379</v>
@@ -63241,10 +63244,10 @@
     </row>
     <row r="84" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="126" t="s">
-        <v>3976</v>
+        <v>3974</v>
       </c>
       <c r="B84" s="122" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
       <c r="C84" s="126" t="s">
         <v>17</v>
@@ -63264,10 +63267,10 @@
     </row>
     <row r="85" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="126" t="s">
-        <v>3978</v>
+        <v>3976</v>
       </c>
       <c r="B85" s="126" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
       <c r="D85" s="90">
         <v>0.5</v>
@@ -63284,10 +63287,10 @@
     </row>
     <row r="86" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="126" t="s">
-        <v>3980</v>
+        <v>3978</v>
       </c>
       <c r="B86" s="122" t="s">
-        <v>3981</v>
+        <v>3979</v>
       </c>
       <c r="C86" s="126" t="s">
         <v>1380</v>
@@ -63307,13 +63310,13 @@
     </row>
     <row r="87" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="126" t="s">
-        <v>3982</v>
+        <v>3980</v>
       </c>
       <c r="B87" s="122" t="s">
-        <v>3983</v>
+        <v>3981</v>
       </c>
       <c r="C87" s="126" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
       <c r="D87" s="90">
         <v>1</v>
@@ -63330,39 +63333,39 @@
     </row>
     <row r="88" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="126" t="s">
-        <v>3984</v>
+        <v>3982</v>
       </c>
       <c r="B88" s="122" t="s">
-        <v>3985</v>
+        <v>3983</v>
       </c>
       <c r="C88" s="127" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D88" s="117" t="s">
-        <v>4111</v>
+        <v>4109</v>
       </c>
       <c r="E88" s="96" t="s">
         <v>3900</v>
       </c>
       <c r="F88" s="182" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G88" s="182" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="126" t="s">
-        <v>3986</v>
+        <v>3984</v>
       </c>
       <c r="B89" s="122" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="C89" s="126" t="s">
         <v>1380</v>
       </c>
       <c r="D89" s="90" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
       <c r="E89" s="96" t="s">
         <v>1749</v>
@@ -63376,16 +63379,16 @@
     </row>
     <row r="90" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="126" t="s">
+        <v>3986</v>
+      </c>
+      <c r="B90" s="122" t="s">
+        <v>3987</v>
+      </c>
+      <c r="C90" s="126" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D90" s="90" t="s">
         <v>3988</v>
-      </c>
-      <c r="B90" s="122" t="s">
-        <v>3989</v>
-      </c>
-      <c r="C90" s="126" t="s">
-        <v>3991</v>
-      </c>
-      <c r="D90" s="90" t="s">
-        <v>3990</v>
       </c>
       <c r="E90" s="96" t="s">
         <v>1749</v>
@@ -63406,7 +63409,7 @@
     </row>
     <row r="93" spans="1:7" s="126" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="118" t="s">
-        <v>3920</v>
+        <v>3918</v>
       </c>
       <c r="B93" s="118"/>
       <c r="C93" s="118"/>
@@ -63417,10 +63420,10 @@
     </row>
     <row r="94" spans="1:7" s="126" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="126" t="s">
-        <v>3919</v>
+        <v>3917</v>
       </c>
       <c r="B94" s="123" t="s">
-        <v>3924</v>
+        <v>3922</v>
       </c>
       <c r="C94" s="126" t="s">
         <v>2511</v>
@@ -63494,13 +63497,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>4151</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>4152</v>
+      </c>
+      <c r="D2" s="51" t="s">
         <v>4153</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>4154</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>4155</v>
       </c>
       <c r="E2" s="51" t="s">
         <v>3900</v>
@@ -63543,25 +63546,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>4156</v>
+        <v>4154</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>4159</v>
+        <v>4157</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D4" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="E4" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F4" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G4" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H4" s="51" t="s">
         <v>1295</v>
@@ -63570,25 +63573,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4157</v>
+        <v>4155</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>4158</v>
+        <v>4156</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="D5" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="E5" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F5" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G5" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H5" s="51" t="s">
         <v>1295</v>
@@ -63597,7 +63600,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>4160</v>
+        <v>4158</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="16"/>
@@ -63656,7 +63659,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>4161</v>
+        <v>4159</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="16"/>
@@ -63675,16 +63678,16 @@
         <v>864</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E10" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F10" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G10" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H10" s="51" t="s">
         <v>1295</v>
@@ -63847,7 +63850,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>4164</v>
+        <v>4162</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="16"/>
@@ -63866,16 +63869,16 @@
         <v>68</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E18" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F18" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G18" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H18" s="51" t="s">
         <v>1295</v>
@@ -63957,16 +63960,16 @@
         <v>870</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E22" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F22" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G22" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H22" s="51" t="s">
         <v>1295</v>
@@ -64224,16 +64227,16 @@
         <v>81</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E33" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F33" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G33" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H33" s="51" t="s">
         <v>1295</v>
@@ -64250,16 +64253,16 @@
         <v>83</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E34" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F34" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G34" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H34" s="51" t="s">
         <v>1295</v>
@@ -64276,16 +64279,16 @@
         <v>85</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E35" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F35" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G35" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H35" s="51" t="s">
         <v>1295</v>
@@ -64302,16 +64305,16 @@
         <v>87</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E36" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F36" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G36" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H36" s="51" t="s">
         <v>1295</v>
@@ -64328,16 +64331,16 @@
         <v>89</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E37" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F37" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G37" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H37" s="51" t="s">
         <v>1295</v>
@@ -64354,16 +64357,16 @@
         <v>91</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E38" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F38" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G38" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H38" s="51" t="s">
         <v>1295</v>
@@ -64380,16 +64383,16 @@
         <v>93</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E39" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F39" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G39" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H39" s="51" t="s">
         <v>1295</v>
@@ -64406,16 +64409,16 @@
         <v>95</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E40" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F40" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G40" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H40" s="51" t="s">
         <v>1295</v>
@@ -64432,16 +64435,16 @@
         <v>96</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E41" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F41" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G41" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H41" s="51" t="s">
         <v>1295</v>
@@ -64458,16 +64461,16 @@
         <v>894</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E42" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F42" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G42" s="177" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="H42" s="51" t="s">
         <v>1295</v>
@@ -64719,7 +64722,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>4162</v>
+        <v>4160</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="16"/>
@@ -64738,16 +64741,16 @@
         <v>98</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E54" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F54" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G54" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H54" s="51" t="s">
         <v>1295</v>
@@ -64913,7 +64916,7 @@
         <v>101</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>4184</v>
+        <v>4182</v>
       </c>
       <c r="E62" s="51" t="s">
         <v>1749</v>
@@ -65060,7 +65063,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>4163</v>
+        <v>4161</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="16"/>
@@ -65079,7 +65082,7 @@
         <v>105</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>4106</v>
+        <v>4104</v>
       </c>
       <c r="E69" s="51" t="s">
         <v>1721</v>
@@ -65671,7 +65674,7 @@
         <v>967</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>4112</v>
+        <v>4110</v>
       </c>
       <c r="E93" s="96" t="s">
         <v>3900</v>
@@ -65715,7 +65718,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>4165</v>
+        <v>4163</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="16"/>
@@ -65734,16 +65737,16 @@
         <v>970</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E96" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F96" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G96" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H96" s="51" t="s">
         <v>1295</v>
@@ -66105,16 +66108,16 @@
         <v>997</v>
       </c>
       <c r="C111" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E111" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F111" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G111" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H111" s="51" t="s">
         <v>1295</v>
@@ -66180,16 +66183,16 @@
         <v>1004</v>
       </c>
       <c r="C114" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E114" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F114" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G114" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H114" s="51" t="s">
         <v>1295</v>
@@ -66359,16 +66362,16 @@
         <v>1021</v>
       </c>
       <c r="C121" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E121" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F121" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G121" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H121" s="51" t="s">
         <v>1295</v>
@@ -66532,16 +66535,16 @@
         <v>1035</v>
       </c>
       <c r="C128" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E128" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F128" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G128" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H128" s="51" t="s">
         <v>1295</v>
@@ -66581,16 +66584,16 @@
         <v>1039</v>
       </c>
       <c r="C130" s="24" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E130" s="51" t="s">
         <v>3900</v>
       </c>
       <c r="F130" s="177" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="G130" s="177" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H130" s="51" t="s">
         <v>1295</v>
@@ -66923,7 +66926,7 @@
         <v>2695</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>4112</v>
+        <v>4110</v>
       </c>
       <c r="D144" s="30">
         <v>5</v>
